--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92C95648-EE6B-43CE-8E05-46079A6D956B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25B8636C-EF87-41D6-8706-DBA684A095F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projecten" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Sarah Mitchell</t>
+  </si>
+  <si>
+    <t>Railing</t>
+  </si>
+  <si>
+    <t>Marcus Rodriguez</t>
+  </si>
+  <si>
+    <t>Stair</t>
+  </si>
+  <si>
+    <t>Emma Chen</t>
+  </si>
+  <si>
+    <t>Stair railing</t>
+  </si>
+  <si>
+    <t>David Thompson</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>Priya Patel</t>
+  </si>
+  <si>
+    <t>Alexander Murphy</t>
+  </si>
+  <si>
+    <t>Sofia Andersson</t>
+  </si>
+  <si>
+    <t>James Williams</t>
+  </si>
+  <si>
+    <t>Aria Nakamura</t>
+  </si>
+  <si>
+    <t>Lucas Brown</t>
+  </si>
   <si>
     <t>Nr</t>
   </si>
@@ -41,90 +95,6 @@
   </si>
   <si>
     <t>Werkomschrijving</t>
-  </si>
-  <si>
-    <t>ELPRO</t>
-  </si>
-  <si>
-    <t>Terrasleuning</t>
-  </si>
-  <si>
-    <t>Maetens</t>
-  </si>
-  <si>
-    <t>Alu buis</t>
-  </si>
-  <si>
-    <t>Platen veranda</t>
-  </si>
-  <si>
-    <t>Brems Leo</t>
-  </si>
-  <si>
-    <t>Deur mechelen</t>
-  </si>
-  <si>
-    <t>Serstevens</t>
-  </si>
-  <si>
-    <t>Sierstuk ingangspoort</t>
-  </si>
-  <si>
-    <t>IBO</t>
-  </si>
-  <si>
-    <t>Terrasleuningen</t>
-  </si>
-  <si>
-    <t>Aras Nobels</t>
-  </si>
-  <si>
-    <t>Handgreep</t>
-  </si>
-  <si>
-    <t>Brems</t>
-  </si>
-  <si>
-    <t>Draaitrap aanpassen</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>Trapleuning</t>
-  </si>
-  <si>
-    <t>Nijns</t>
-  </si>
-  <si>
-    <t>Trapleuningen</t>
-  </si>
-  <si>
-    <t>De Buyser</t>
-  </si>
-  <si>
-    <t>Metriek</t>
-  </si>
-  <si>
-    <t>De Groef</t>
-  </si>
-  <si>
-    <t>3 kolommen</t>
-  </si>
-  <si>
-    <t>De Ridder</t>
-  </si>
-  <si>
-    <t>De Wachter</t>
-  </si>
-  <si>
-    <t>TRAEN</t>
-  </si>
-  <si>
-    <t>Poort</t>
-  </si>
-  <si>
-    <t>Caremans</t>
   </si>
   <si>
     <t>JP</t>
@@ -203,17 +173,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -224,6 +279,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B95C3B4E-034C-4D38-A72A-80AF4393B50C}" name="Table1" displayName="Table1" ref="A1:B57" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3" headerRowBorderDxfId="2" headerRowCellStyle="Heading 1">
+  <autoFilter ref="A1:B57" xr:uid="{B95C3B4E-034C-4D38-A72A-80AF4393B50C}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{E919FD24-3695-45A5-BD39-850C8D666C37}" name="Id" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{FA86FFF2-4D29-476E-8031-FECF1E6A0DFC}" name="Customer" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,8 +593,8 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="65.5703125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -554,25 +620,25 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="26.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" ht="26.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -583,140 +649,132 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="26.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="26.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" ht="26.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="26.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="26.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="26.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
+      <c r="B12" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="26.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>18</v>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="26.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
+      <c r="B14" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="26.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>22</v>
+      <c r="B15" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="26.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>23</v>
+      <c r="B16" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="26.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="26.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="26.25">
       <c r="A19" s="2">
@@ -729,23 +787,15 @@
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="26.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="26.25">
       <c r="A22" s="2">
@@ -758,12 +808,8 @@
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="26.25">
       <c r="A24" s="2">
@@ -1005,6 +1051,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1021,22 +1070,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.25">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
